--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20353.92</v>
+        <v>20417.96</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>36896.08</v>
+        <v>37246.62</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29776.2</v>
+        <v>29981.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2568.67</v>
+        <v>2586.41</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4931.85</v>
+        <v>4965.9</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30364.1</v>
+        <v>30573.74</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15191.8</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>47454.61</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>30600.16</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>47835.83</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>16923.85</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38308.75</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9026.91</v>
+        <v>8882.17</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>25140.58</v>
+        <v>25308.85</v>
       </c>
     </row>
   </sheetData>
